--- a/99_Others/Bug_Management.xlsx
+++ b/99_Others/Bug_Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6FE688-DBEA-4289-8F4D-096DBF665E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E64672E-0CCA-4F7C-891F-3EC0A88C9E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0CEC575C-2CE2-4A91-9FC5-0346F782D22B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -394,6 +394,35 @@
     <rPh sb="7" eb="9">
       <t>カンリ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリ起動時のデータベース接続失敗時の例外処理がない</t>
+    <rPh sb="3" eb="5">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>？</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -893,7 +922,7 @@
     <col min="3" max="3" width="6.75" customWidth="1"/>
     <col min="4" max="4" width="80.375" customWidth="1"/>
     <col min="5" max="5" width="71" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="7.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.125" customWidth="1"/>
     <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
@@ -1006,14 +1035,24 @@
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="7">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="F9" s="5">
+        <v>46034</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
@@ -1125,7 +1164,7 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
         <f ca="1">_xlfn.CONCAT("PDF出力・印刷日："&amp;TEXT(TODAY(),"YYYY/MM/DD"))</f>
-        <v>PDF出力・印刷日：2026/01/04</v>
+        <v>PDF出力・印刷日：2026/01/12</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>

--- a/99_Others/Bug_Management.xlsx
+++ b/99_Others/Bug_Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\99_Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E64672E-0CCA-4F7C-891F-3EC0A88C9E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B5DB50-D942-4C4F-A93F-FBB8F7915C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0CEC575C-2CE2-4A91-9FC5-0346F782D22B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -423,6 +423,16 @@
   </si>
   <si>
     <t>？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Long型のフィールドに値をいれると400エラーになる</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1060,8 +1070,12 @@
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="7">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1075,7 +1089,9 @@
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="7">
+        <v>5</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1090,7 +1106,9 @@
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="7">
+        <v>5</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1105,7 +1123,9 @@
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="7">
+        <v>5</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1164,7 +1184,7 @@
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
         <f ca="1">_xlfn.CONCAT("PDF出力・印刷日："&amp;TEXT(TODAY(),"YYYY/MM/DD"))</f>
-        <v>PDF出力・印刷日：2026/01/12</v>
+        <v>PDF出力・印刷日：2026/01/13</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
